--- a/etf_holdings/2026-08-27_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:24</t>
+          <t>2026-08-27 16:55:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:24</t>
+          <t>2026-08-27 16:55:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:24</t>
+          <t>2026-08-27 16:55:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:24</t>
+          <t>2026-08-27 16:55:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:24</t>
+          <t>2026-08-27 16:55:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:24</t>
+          <t>2026-08-27 16:55:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:24</t>
+          <t>2026-08-27 16:55:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:24</t>
+          <t>2026-08-27 16:55:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:24</t>
+          <t>2026-08-27 16:55:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:24</t>
+          <t>2026-08-27 16:55:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:24</t>
+          <t>2026-08-27 16:55:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:24</t>
+          <t>2026-08-27 16:55:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:24</t>
+          <t>2026-08-27 16:55:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:24</t>
+          <t>2026-08-27 16:55:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:24</t>
+          <t>2026-08-27 16:55:59</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:26</t>
+          <t>2026-08-27 16:56:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:26</t>
+          <t>2026-08-27 16:56:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:26</t>
+          <t>2026-08-27 16:56:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:26</t>
+          <t>2026-08-27 16:56:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:26</t>
+          <t>2026-08-27 16:56:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:26</t>
+          <t>2026-08-27 16:56:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:26</t>
+          <t>2026-08-27 16:56:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:26</t>
+          <t>2026-08-27 16:56:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:26</t>
+          <t>2026-08-27 16:56:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:26</t>
+          <t>2026-08-27 16:56:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:26</t>
+          <t>2026-08-27 16:56:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:26</t>
+          <t>2026-08-27 16:56:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:26</t>
+          <t>2026-08-27 16:56:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:26</t>
+          <t>2026-08-27 16:56:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:26</t>
+          <t>2026-08-27 16:56:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:27</t>
+          <t>2026-08-27 16:56:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:27</t>
+          <t>2026-08-27 16:56:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:27</t>
+          <t>2026-08-27 16:56:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:27</t>
+          <t>2026-08-27 16:56:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:27</t>
+          <t>2026-08-27 16:56:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:27</t>
+          <t>2026-08-27 16:56:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:27</t>
+          <t>2026-08-27 16:56:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:27</t>
+          <t>2026-08-27 16:56:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:27</t>
+          <t>2026-08-27 16:56:02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:27</t>
+          <t>2026-08-27 16:56:02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:27</t>
+          <t>2026-08-27 16:56:02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:27</t>
+          <t>2026-08-27 16:56:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:27</t>
+          <t>2026-08-27 16:56:02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:27</t>
+          <t>2026-08-27 16:56:02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:27</t>
+          <t>2026-08-27 16:56:02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:28</t>
+          <t>2026-08-27 16:56:03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:28</t>
+          <t>2026-08-27 16:56:03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:28</t>
+          <t>2026-08-27 16:56:03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:28</t>
+          <t>2026-08-27 16:56:03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:28</t>
+          <t>2026-08-27 16:56:03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:28</t>
+          <t>2026-08-27 16:56:03</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:28</t>
+          <t>2026-08-27 16:56:03</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:28</t>
+          <t>2026-08-27 16:56:03</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:28</t>
+          <t>2026-08-27 16:56:03</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:28</t>
+          <t>2026-08-27 16:56:03</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:28</t>
+          <t>2026-08-27 16:56:03</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:28</t>
+          <t>2026-08-27 16:56:03</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:28</t>
+          <t>2026-08-27 16:56:03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:28</t>
+          <t>2026-08-27 16:56:03</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-27_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00982A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:59</t>
+          <t>2026-08-27 17:13:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.50%1,794,000</t>
+          <t>8.49%1,794,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8.49%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:59</t>
+          <t>2026-08-27 17:13:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.79%510,000</t>
+          <t>6.83%510,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.79%</t>
+          <t>6.83%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:59</t>
+          <t>2026-08-27 17:13:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.75%872,000</t>
+          <t>6.62%872,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.75%</t>
+          <t>6.62%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:59</t>
+          <t>2026-08-27 17:13:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,16 +705,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.04%3,850,000</t>
+          <t>5.88%3,820,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>5.88%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3850000</v>
+        <v>3820000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:59</t>
+          <t>2026-08-27 17:13:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,16 +766,16 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.30%186,000</t>
+          <t>5.21%185,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.30%</t>
+          <t>5.21%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>186000</v>
+        <v>185000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:59</t>
+          <t>2026-08-27 17:13:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.82%4,809,000</t>
+          <t>4.21%4,809,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>4.21%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:59</t>
+          <t>2026-08-27 17:13:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.7%5500</t>
+          <t>+9.94%6915</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5500</v>
+        <v>6915</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.72%322,000</t>
+          <t>3.48%256,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.48%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>322000</v>
+        <v>256000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:59</t>
+          <t>2026-08-27 17:13:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.51%1990</t>
+          <t>-6.7%5500</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1990</v>
+        <v>5500</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.30%849,000</t>
+          <t>3.45%319,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.45%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>849000</v>
+        <v>319000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:59</t>
+          <t>2026-08-27 17:13:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+9.94%6915</t>
+          <t>+5.95%1425</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+5.95%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6915</v>
+        <v>1425</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.18%258,000</t>
+          <t>3.30%1,180,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>258000</v>
+        <v>1180000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:59</t>
+          <t>2026-08-27 17:13:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.99%5090</t>
+          <t>+0.51%1990</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5090</v>
+        <v>1990</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.04%307,000</t>
+          <t>3.29%842,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>307000</v>
+        <v>842000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:59</t>
+          <t>2026-08-27 17:13:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.11%917</t>
+          <t>+0.99%5090</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>917</v>
+        <v>5090</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.97%1,650,000</t>
+          <t>3.07%307,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1650000</v>
+        <v>307000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:59</t>
+          <t>2026-08-27 17:13:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.93%727,000</t>
+          <t>2.98%727,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:59</t>
+          <t>2026-08-27 17:13:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.82%3,178,000</t>
+          <t>2.98%3,178,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:59</t>
+          <t>2026-08-27 17:13:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+5.95%1425</t>
+          <t>+0.11%917</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+5.95%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1425</v>
+        <v>917</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.64%1,000,000</t>
+          <t>2.97%1,650,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.97%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1000000</v>
+        <v>1650000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 16:55:59</t>
+          <t>2026-08-27 17:13:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,20 +1376,20 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.36%381,000</t>
+          <t>2.48%378,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.48%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>381000</v>
+        <v>378000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:00</t>
+          <t>2026-08-27 17:13:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,16 +1437,16 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.09%1,123,000</t>
+          <t>2.10%1,114,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.10%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1123000</v>
+        <v>1114000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:00</t>
+          <t>2026-08-27 17:13:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,16 +1498,16 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.01%1,486,000</t>
+          <t>1.96%1,478,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1486000</v>
+        <v>1478000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:00</t>
+          <t>2026-08-27 17:13:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1559,16 +1559,16 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.99%3,302,000</t>
+          <t>1.94%3,284,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3302000</v>
+        <v>3284000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:00</t>
+          <t>2026-08-27 17:13:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.68%1,158,000</t>
+          <t>1.73%1,158,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:00</t>
+          <t>2026-08-27 17:13:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.33%1,581,000</t>
+          <t>1.33%1,569,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1581000</v>
+        <v>1569000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:00</t>
+          <t>2026-08-27 17:13:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>5483中美晶</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-5.56%1445</t>
+          <t>+1.11%182</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1445</v>
+        <v>182</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.31%437,000</t>
+          <t>1.26%3,524,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>437000</v>
+        <v>3524000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:00</t>
+          <t>2026-08-27 17:13:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>6214精誠</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-4.05%118.5</t>
+          <t>+0.83%182.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>118.5</v>
+        <v>182.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.29%5,315,000</t>
+          <t>1.25%3,494,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>5315000</v>
+        <v>3494000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:00</t>
+          <t>2026-08-27 17:13:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1864,16 +1864,16 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.26%4,412,000</t>
+          <t>1.25%4,375,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>4412000</v>
+        <v>4375000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:00</t>
+          <t>2026-08-27 17:13:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5483中美晶</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+1.11%182</t>
+          <t>-5.56%1445</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>182</v>
+        <v>1445</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.25%3,552,000</t>
+          <t>1.23%433,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>3552000</v>
+        <v>433000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:00</t>
+          <t>2026-08-27 17:13:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6214精誠</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+0.83%182.5</t>
+          <t>-4.05%118.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>-4.05%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>182.5</v>
+        <v>118.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.25%3,524,000</t>
+          <t>1.23%5,270,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>3524000</v>
+        <v>5270000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:00</t>
+          <t>2026-08-27 17:13:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2047,16 +2047,16 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.25%1,811,000</t>
+          <t>1.22%1,796,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1811000</v>
+        <v>1796000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:00</t>
+          <t>2026-08-27 17:13:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2108,16 +2108,16 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.23%3,453,000</t>
+          <t>1.21%3,424,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>3453000</v>
+        <v>3424000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:00</t>
+          <t>2026-08-27 17:13:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2169,16 +2169,16 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.19%3,494,000</t>
+          <t>1.20%3,464,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>3494000</v>
+        <v>3464000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:00</t>
+          <t>2026-08-27 17:13:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.17%2,371,000</t>
+          <t>1.17%2,350,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>2371000</v>
+        <v>2350000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:00</t>
+          <t>2026-08-27 17:13:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>2467志聖</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+2.2%605</t>
+          <t>+2.63%585</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+2.63%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>605</v>
+        <v>585</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.12%965,000</t>
+          <t>1.15%1,000,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>965000</v>
+        <v>1000000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:02</t>
+          <t>2026-08-27 17:13:50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2467志聖</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+2.63%585</t>
+          <t>+2.2%605</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+2.63%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.12%1,000,000</t>
+          <t>1.14%956,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1000000</v>
+        <v>956000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:02</t>
+          <t>2026-08-27 17:13:50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2413,16 +2413,16 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.11%3,416,000</t>
+          <t>1.12%3,388,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>3416000</v>
+        <v>3388000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:02</t>
+          <t>2026-08-27 17:13:50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2478大毅</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.45%15305</t>
+          <t>+2.46%125</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.45%</t>
+          <t>+2.46%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>15305</v>
+        <v>125</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.11%35,900</t>
+          <t>1.10%4,475,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>35900</v>
+        <v>4475000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:02</t>
+          <t>2026-08-27 17:13:50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2478大毅</t>
+          <t>5425台半</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+2.46%125</t>
+          <t>-1.45%95.2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+2.46%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>125</v>
+        <v>95.2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.08%4,511,000</t>
+          <t>1.09%5,824,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>4511000</v>
+        <v>5824000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:02</t>
+          <t>2026-08-27 17:13:50</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-3.15%277</t>
+          <t>-2.45%15305</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-3.15%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>277</v>
+        <v>15305</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.07%1,910,000</t>
+          <t>1.08%35,900</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1910000</v>
+        <v>35900</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:02</t>
+          <t>2026-08-27 17:13:50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6472保瑞</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-3.83%439.5</t>
+          <t>-3.15%277</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.83%</t>
+          <t>-3.15%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>439.5</v>
+        <v>277</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.93%1,032,000</t>
+          <t>1.04%1,910,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1032000</v>
+        <v>1910000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:02</t>
+          <t>2026-08-27 17:13:50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.90%382,000</t>
+          <t>0.98%382,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:02</t>
+          <t>2026-08-27 17:13:50</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2486一詮</t>
+          <t>6472保瑞</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.33%259</t>
+          <t>-3.83%439.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-3.83%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>259</v>
+        <v>439.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.83%1,607,000</t>
+          <t>0.89%1,032,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1607000</v>
+        <v>1032000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:02</t>
+          <t>2026-08-27 17:13:50</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5536聖暉*</t>
+          <t>2486一詮</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0%854</t>
+          <t>-1.33%259</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>854</v>
+        <v>259</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.77%459,000</t>
+          <t>0.82%1,607,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>459000</v>
+        <v>1607000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:02</t>
+          <t>2026-08-27 17:13:50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>5536聖暉*</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+9.96%2650</t>
+          <t>0%854</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2650</v>
+        <v>854</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.44%93,000</t>
+          <t>0.77%459,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>93000</v>
+        <v>459000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:02</t>
+          <t>2026-08-27 17:13:50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.92%219.5</t>
+          <t>+9.96%2650</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>+9.96%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>219.5</v>
+        <v>2650</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.44%1,021,000</t>
+          <t>0.48%93,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1021000</v>
+        <v>93000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:02</t>
+          <t>2026-08-27 17:13:50</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5425台半</t>
+          <t>2476鉅祥</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.45%95.2</t>
+          <t>+0.8%126.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+0.8%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>95.2</v>
+        <v>126.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.43%2,249,000</t>
+          <t>0.32%1,301,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>2249000</v>
+        <v>1301000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:02</t>
+          <t>2026-08-27 17:13:50</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-3.43%563</t>
+          <t>-0.5%497.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-3.43%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>563</v>
+        <v>497.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.37%322,000</t>
+          <t>0.30%309,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>322000</v>
+        <v>309000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:02</t>
+          <t>2026-08-27 17:13:50</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2476鉅祥</t>
+          <t>6672騰輝電子-KY</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.8%126.5</t>
+          <t>+1.81%281.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>+1.81%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>126.5</v>
+        <v>281.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.32%1,311,000</t>
+          <t>0.30%544,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1311000</v>
+        <v>544000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:02</t>
+          <t>2026-08-27 17:13:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,34 +3188,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>3617碩天</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.5%497.5</t>
+          <t>-1.19%248.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>497.5</v>
+        <v>248.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.31%312,000</t>
+          <t>0.29%599,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>312000</v>
+        <v>599000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:03</t>
+          <t>2026-08-27 17:13:51</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,34 +3249,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3617碩天</t>
+          <t>8070長華*</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.19%248.5</t>
+          <t>-1.17%50.7</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>248.5</v>
+        <v>50.7</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.30%612,000</t>
+          <t>0.28%2,862,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>612000</v>
+        <v>2862000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:03</t>
+          <t>2026-08-27 17:13:51</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6672騰輝電子-KY</t>
+          <t>2885元大金</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+1.81%281.5</t>
+          <t>+0.64%63.2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+1.81%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>281.5</v>
+        <v>63.2</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.30%549,000</t>
+          <t>0.27%2,213,556</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>549000</v>
+        <v>2213556</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:03</t>
+          <t>2026-08-27 17:13:51</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,34 +3371,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8070長華*</t>
+          <t>6446藥華藥</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.17%50.7</t>
+          <t>-1.58%1560</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>50.7</v>
+        <v>1560</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.29%2,897,000</t>
+          <t>0.13%42,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>2897000</v>
+        <v>42000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:03</t>
+          <t>2026-08-27 17:13:51</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2885元大金</t>
+          <t>6177達麗</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+0.64%63.2</t>
+          <t>-0.93%47.9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>63.2</v>
+        <v>47.9</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.27%2,213,556</t>
+          <t>0.02%194,350</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>2213556</v>
+        <v>194350</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:03</t>
+          <t>2026-08-27 17:13:51</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,34 +3493,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>6446藥華藥</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-1.58%1560</t>
+          <t>-3.35%5920</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>-3.35%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1560</v>
+        <v>5920</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.13%42,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>42000</v>
+        <v>1000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:03</t>
+          <t>2026-08-27 17:13:51</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3554,38 +3554,38 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6177達麗</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-0.93%47.9</t>
+          <t>+9.75%1295</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>+9.75%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>47.9</v>
+        <v>1295</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.02%194,350</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>194350</v>
+        <v>1000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:03</t>
+          <t>2026-08-27 17:13:51</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3615,38 +3615,38 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>4441振大環球</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-3.35%5920</t>
+          <t>+1.13%178.5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-3.35%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>5920</v>
+        <v>178.5</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.01%1,000</t>
+          <t>&lt;0.01%4,000</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:03</t>
+          <t>2026-08-27 17:13:51</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3676,25 +3676,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>1519華城</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>+9.75%1295</t>
+          <t>+7.39%770</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>+9.75%</t>
+          <t>+7.39%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1295</v>
+        <v>770</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%660</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:03</t>
+          <t>2026-08-27 17:13:51</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3737,25 +3737,25 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>4441振大環球</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>+1.13%178.5</t>
+          <t>+9.9%494</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+9.9%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>178.5</v>
+        <v>494</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>&lt;0.01%4,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:03</t>
+          <t>2026-08-27 17:13:51</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3798,25 +3798,25 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1519華城</t>
+          <t>3706神達</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>+7.39%770</t>
+          <t>-0.11%91.4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>+7.39%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>770</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>&lt;0.01%660</t>
+          <t>&lt;0.01%1,400</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3825,11 +3825,11 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>660</v>
+        <v>1400</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:03</t>
+          <t>2026-08-27 17:13:51</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3859,30 +3859,30 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>2886兆豐金</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>+9.9%494</t>
+          <t>-0.97%46.15</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>+9.9%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>494</v>
+        <v>46.15</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-27 16:56:03</t>
+          <t>2026-08-27 17:13:51</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3920,163 +3920,41 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3706神達</t>
+          <t>2881富邦金</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-0.11%91.4</t>
+          <t>+2.17%141.5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>91.40000000000001</v>
+        <v>141.5</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,400</t>
+          <t>0%250</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>1400</v>
+        <v>250</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-08-27 16:56:03</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2886兆豐金</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-0.97%46.15</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>-0.97%</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>46.15</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>0%1,000</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-08-27 16:56:03</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2881富邦金</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>+2.17%141.5</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>+2.17%</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>141.5</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>0%250</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K60" t="n">
-        <v>250</v>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-08-27_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:47</t>
+          <t>2026-08-27 19:37:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:47</t>
+          <t>2026-08-27 19:37:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:47</t>
+          <t>2026-08-27 19:37:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:47</t>
+          <t>2026-08-27 19:37:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:47</t>
+          <t>2026-08-27 19:37:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:47</t>
+          <t>2026-08-27 19:37:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:47</t>
+          <t>2026-08-27 19:37:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:47</t>
+          <t>2026-08-27 19:37:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:47</t>
+          <t>2026-08-27 19:37:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:47</t>
+          <t>2026-08-27 19:37:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:47</t>
+          <t>2026-08-27 19:37:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:47</t>
+          <t>2026-08-27 19:37:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:47</t>
+          <t>2026-08-27 19:37:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:47</t>
+          <t>2026-08-27 19:37:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:47</t>
+          <t>2026-08-27 19:37:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:48</t>
+          <t>2026-08-27 19:37:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:48</t>
+          <t>2026-08-27 19:37:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:48</t>
+          <t>2026-08-27 19:37:47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:48</t>
+          <t>2026-08-27 19:37:47</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:48</t>
+          <t>2026-08-27 19:37:47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:48</t>
+          <t>2026-08-27 19:37:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:48</t>
+          <t>2026-08-27 19:37:47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:48</t>
+          <t>2026-08-27 19:37:47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:48</t>
+          <t>2026-08-27 19:37:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:48</t>
+          <t>2026-08-27 19:37:47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:48</t>
+          <t>2026-08-27 19:37:47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:48</t>
+          <t>2026-08-27 19:37:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:48</t>
+          <t>2026-08-27 19:37:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:48</t>
+          <t>2026-08-27 19:37:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:48</t>
+          <t>2026-08-27 19:37:47</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:50</t>
+          <t>2026-08-27 19:37:48</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:50</t>
+          <t>2026-08-27 19:37:48</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:50</t>
+          <t>2026-08-27 19:37:48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:50</t>
+          <t>2026-08-27 19:37:48</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:50</t>
+          <t>2026-08-27 19:37:48</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:50</t>
+          <t>2026-08-27 19:37:48</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:50</t>
+          <t>2026-08-27 19:37:48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:50</t>
+          <t>2026-08-27 19:37:48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:50</t>
+          <t>2026-08-27 19:37:48</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:50</t>
+          <t>2026-08-27 19:37:48</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:50</t>
+          <t>2026-08-27 19:37:48</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:50</t>
+          <t>2026-08-27 19:37:48</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:50</t>
+          <t>2026-08-27 19:37:48</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:50</t>
+          <t>2026-08-27 19:37:48</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:50</t>
+          <t>2026-08-27 19:37:48</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:51</t>
+          <t>2026-08-27 19:37:49</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:51</t>
+          <t>2026-08-27 19:37:49</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:51</t>
+          <t>2026-08-27 19:37:49</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:51</t>
+          <t>2026-08-27 19:37:49</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:51</t>
+          <t>2026-08-27 19:37:49</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:51</t>
+          <t>2026-08-27 19:37:49</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:51</t>
+          <t>2026-08-27 19:37:49</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:51</t>
+          <t>2026-08-27 19:37:49</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:51</t>
+          <t>2026-08-27 19:37:49</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:51</t>
+          <t>2026-08-27 19:37:49</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:51</t>
+          <t>2026-08-27 19:37:49</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:51</t>
+          <t>2026-08-27 19:37:49</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-08-27_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:45</t>
+          <t>2026-08-27 22:48:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:45</t>
+          <t>2026-08-27 22:48:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:45</t>
+          <t>2026-08-27 22:48:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:45</t>
+          <t>2026-08-27 22:48:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:45</t>
+          <t>2026-08-27 22:48:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:45</t>
+          <t>2026-08-27 22:48:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:45</t>
+          <t>2026-08-27 22:48:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:45</t>
+          <t>2026-08-27 22:48:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:45</t>
+          <t>2026-08-27 22:48:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:45</t>
+          <t>2026-08-27 22:48:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:45</t>
+          <t>2026-08-27 22:48:12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:45</t>
+          <t>2026-08-27 22:48:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:45</t>
+          <t>2026-08-27 22:48:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:45</t>
+          <t>2026-08-27 22:48:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:45</t>
+          <t>2026-08-27 22:48:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:47</t>
+          <t>2026-08-27 22:48:13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:47</t>
+          <t>2026-08-27 22:48:13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:47</t>
+          <t>2026-08-27 22:48:13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:47</t>
+          <t>2026-08-27 22:48:13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:47</t>
+          <t>2026-08-27 22:48:13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:47</t>
+          <t>2026-08-27 22:48:13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:47</t>
+          <t>2026-08-27 22:48:13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:47</t>
+          <t>2026-08-27 22:48:13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:47</t>
+          <t>2026-08-27 22:48:13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:47</t>
+          <t>2026-08-27 22:48:13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:47</t>
+          <t>2026-08-27 22:48:13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:47</t>
+          <t>2026-08-27 22:48:13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:47</t>
+          <t>2026-08-27 22:48:13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:47</t>
+          <t>2026-08-27 22:48:13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:47</t>
+          <t>2026-08-27 22:48:13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:48</t>
+          <t>2026-08-27 22:48:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:48</t>
+          <t>2026-08-27 22:48:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:48</t>
+          <t>2026-08-27 22:48:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:48</t>
+          <t>2026-08-27 22:48:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:48</t>
+          <t>2026-08-27 22:48:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:48</t>
+          <t>2026-08-27 22:48:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:48</t>
+          <t>2026-08-27 22:48:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:48</t>
+          <t>2026-08-27 22:48:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:48</t>
+          <t>2026-08-27 22:48:15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:48</t>
+          <t>2026-08-27 22:48:15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:48</t>
+          <t>2026-08-27 22:48:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:48</t>
+          <t>2026-08-27 22:48:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:48</t>
+          <t>2026-08-27 22:48:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:48</t>
+          <t>2026-08-27 22:48:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:48</t>
+          <t>2026-08-27 22:48:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:49</t>
+          <t>2026-08-27 22:48:16</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:49</t>
+          <t>2026-08-27 22:48:16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:49</t>
+          <t>2026-08-27 22:48:16</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:49</t>
+          <t>2026-08-27 22:48:16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:49</t>
+          <t>2026-08-27 22:48:16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:49</t>
+          <t>2026-08-27 22:48:16</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:49</t>
+          <t>2026-08-27 22:48:16</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:49</t>
+          <t>2026-08-27 22:48:16</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:49</t>
+          <t>2026-08-27 22:48:16</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:49</t>
+          <t>2026-08-27 22:48:16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:49</t>
+          <t>2026-08-27 22:48:16</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:49</t>
+          <t>2026-08-27 22:48:16</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
